--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyWeakness" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyWeakness" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyWeakness</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>870aaf67d9d93423</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>variant_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>element</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>enum&lt;CombatElement&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..7</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,106 +407,751 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyWeakness</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>870aaf67d9d93423</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyVariant.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enum&lt;CombatElement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>101</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>101</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>102</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>102</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>103</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>103</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>104</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>104</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>105</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>105</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>105</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>106</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>106</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>106</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>107</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>107</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>107</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>108</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>108</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>108</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>109</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>109</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>110</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>110</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>111</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>111</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>111</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>95</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>95</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>95</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>96</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>96</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>96</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>97</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>97</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>98</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>98</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>98</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>99</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>99</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>99</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,45 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,45 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,45 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1271,6 +1271,45 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1310,6 +1310,45 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,6 +1349,45 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,45 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,6 +1427,45 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1466,6 +1466,45 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1505,6 +1505,45 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1544,45 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,49 +974,49 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1039,36 +1039,36 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1091,20 +1091,20 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C49" t="n">
         <v>3</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1130,33 +1130,33 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
@@ -1182,23 +1182,23 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1208,98 +1208,98 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C61" t="n">
         <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
@@ -1338,20 +1338,20 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C67" t="n">
         <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -1364,98 +1364,98 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -1481,23 +1481,23 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1507,46 +1507,46 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1070001</v>
+        <v>1090002</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1070001</v>
+        <v>1090003</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1070001</v>
+        <v>1090004</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1080001</v>
+        <v>1090011</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -1559,25 +1559,389 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1080001</v>
+        <v>1090010</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>96</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>95</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>96</v>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>95</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>96</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,176 +571,176 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
@@ -753,85 +753,85 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -844,62 +844,62 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -909,189 +909,189 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C48" t="n">
         <v>2</v>
@@ -1104,36 +1104,36 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1156,36 +1156,36 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1195,153 +1195,153 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C61" t="n">
         <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1351,209 +1351,209 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1060001</v>
+        <v>1090002</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1060001</v>
+        <v>1090003</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1070001</v>
+        <v>1090004</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1070001</v>
+        <v>1090011</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1070001</v>
+        <v>1090010</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1090002</v>
+        <v>1090011</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1090003</v>
+        <v>1090008</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1090004</v>
+        <v>1090009</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090011</v>
+        <v>1090004</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -1562,128 +1562,128 @@
         <v>1090010</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>95</v>
+        <v>1090006</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090002</v>
+        <v>1090012</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090003</v>
+        <v>96</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1090011</v>
+        <v>1090008</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1090008</v>
+        <v>1090009</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1090009</v>
+        <v>95</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1090004</v>
+        <v>1090010</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090006</v>
+        <v>1090005</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1692,256 +1692,568 @@
         <v>1090012</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090008</v>
+        <v>1090005</v>
       </c>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1090009</v>
+        <v>1090006</v>
       </c>
       <c r="C97" t="n">
         <v>2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C98" t="n">
         <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1090010</v>
+        <v>95</v>
       </c>
       <c r="C99" t="n">
         <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1090011</v>
+        <v>1090002</v>
       </c>
       <c r="C100" t="n">
         <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1090005</v>
+        <v>1090003</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1090012</v>
+        <v>1090004</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C103" t="n">
         <v>3</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1090005</v>
+        <v>1090009</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>96</v>
+        <v>1100003</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>95</v>
+        <v>1100004</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1090002</v>
+        <v>1100009</v>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1090003</v>
+        <v>1100010</v>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1090004</v>
+        <v>100</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1090006</v>
+        <v>1100002</v>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1090009</v>
+        <v>1100007</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>100</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>97</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>99</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>97</v>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>100</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>99</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,46 +597,46 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -649,202 +649,202 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -857,101 +857,101 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -961,257 +961,257 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1221,300 +1221,300 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1060001</v>
+        <v>1090002</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1070001</v>
+        <v>1090003</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1070001</v>
+        <v>1090004</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1070001</v>
+        <v>1090011</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1080001</v>
+        <v>1090010</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1090004</v>
+        <v>1090008</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1090011</v>
+        <v>1090009</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1090010</v>
+        <v>1090004</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>95</v>
+        <v>1090010</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090002</v>
+        <v>1090006</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1090003</v>
+        <v>1090012</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1090011</v>
+        <v>96</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -1523,11 +1523,11 @@
         <v>1090008</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -1536,24 +1536,24 @@
         <v>1090009</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090004</v>
+        <v>95</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -1562,20 +1562,20 @@
         <v>1090010</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090006</v>
+        <v>1090011</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -1585,27 +1585,27 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090012</v>
+        <v>1090005</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>96</v>
+        <v>1090012</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1614,128 +1614,128 @@
         <v>1090008</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1090009</v>
+        <v>1090005</v>
       </c>
       <c r="C89" t="n">
         <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>95</v>
+        <v>1090006</v>
       </c>
       <c r="C90" t="n">
         <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1090010</v>
+        <v>96</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090011</v>
+        <v>95</v>
       </c>
       <c r="C92" t="n">
         <v>3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090005</v>
+        <v>1090002</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1090012</v>
+        <v>1090003</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1090008</v>
+        <v>1090004</v>
       </c>
       <c r="C95" t="n">
         <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
@@ -1744,271 +1744,271 @@
         <v>96</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>95</v>
+        <v>1100003</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1090002</v>
+        <v>1100004</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1090003</v>
+        <v>1100009</v>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1090004</v>
+        <v>1100010</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090006</v>
+        <v>100</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1090009</v>
+        <v>1100002</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>96</v>
+        <v>1100007</v>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1100003</v>
+        <v>99</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1100004</v>
+        <v>1100006</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1100009</v>
+        <v>1100011</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1100010</v>
+        <v>100</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>100</v>
+        <v>1100003</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1100002</v>
+        <v>1100007</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1100007</v>
+        <v>1100012</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1100006</v>
+        <v>1100004</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1100011</v>
+        <v>1100009</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>100</v>
+        <v>1100010</v>
       </c>
       <c r="C116" t="n">
         <v>2</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1100003</v>
+        <v>1100011</v>
       </c>
       <c r="C117" t="n">
         <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="C118" t="n">
         <v>2</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -2017,124 +2017,124 @@
         <v>1100012</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1100004</v>
+        <v>1100002</v>
       </c>
       <c r="C121" t="n">
         <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1100009</v>
+        <v>97</v>
       </c>
       <c r="C122" t="n">
         <v>2</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1100010</v>
+        <v>100</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1100011</v>
+        <v>1100003</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1100006</v>
+        <v>1100004</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1100012</v>
+        <v>1100007</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>99</v>
+        <v>1100009</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1100002</v>
+        <v>1100010</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>97</v>
+        <v>1100012</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C130" t="n">
         <v>3</v>
@@ -2170,90 +2170,389 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1100003</v>
+        <v>104</v>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1100004</v>
+        <v>1110003</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1100007</v>
+        <v>1110004</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1100009</v>
+        <v>1110009</v>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1100010</v>
+        <v>1110011</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1100012</v>
+        <v>103</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>99</v>
+        <v>1110001</v>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D137" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>102</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C141" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>102</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>103</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>102</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>104</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,20 +636,20 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
@@ -662,189 +662,189 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>109</v>
+        <v>980001</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -857,59 +857,59 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -922,46 +922,46 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -974,101 +974,101 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1091,36 +1091,36 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1130,33 +1130,33 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -1169,23 +1169,23 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1060001</v>
+        <v>1090002</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1208,131 +1208,131 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1060001</v>
+        <v>1090003</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1060001</v>
+        <v>1090004</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1070001</v>
+        <v>1090011</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1070001</v>
+        <v>1090010</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1080001</v>
+        <v>1090011</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1090002</v>
+        <v>1090008</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1090003</v>
+        <v>1090009</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -1341,206 +1341,206 @@
         <v>1090004</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1090011</v>
+        <v>1090010</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1090010</v>
+        <v>1090006</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>95</v>
+        <v>1090012</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1090002</v>
+        <v>96</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1090003</v>
+        <v>1090008</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1090011</v>
+        <v>1090009</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1090008</v>
+        <v>95</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1090004</v>
+        <v>1090011</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1090010</v>
+        <v>1090005</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090006</v>
+        <v>1090012</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1090012</v>
+        <v>1090008</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>96</v>
+        <v>1090005</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1090009</v>
+        <v>96</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
@@ -1549,323 +1549,323 @@
         <v>95</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1090010</v>
+        <v>1090002</v>
       </c>
       <c r="C84" t="n">
         <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090011</v>
+        <v>1090003</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090012</v>
+        <v>1090006</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1090008</v>
+        <v>1090009</v>
       </c>
       <c r="C88" t="n">
         <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1090006</v>
+        <v>1100003</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>96</v>
+        <v>1100004</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>95</v>
+        <v>1100009</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090002</v>
+        <v>1100010</v>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1090003</v>
+        <v>100</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1090004</v>
+        <v>1100002</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090006</v>
+        <v>1100007</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1090009</v>
+        <v>99</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>96</v>
+        <v>1100006</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1100003</v>
+        <v>1100011</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1100009</v>
+        <v>1100003</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>100</v>
+        <v>1100012</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1100002</v>
+        <v>97</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1100007</v>
+        <v>1100004</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>99</v>
+        <v>1100009</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1100006</v>
+        <v>1100010</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -1874,63 +1874,63 @@
         <v>1100011</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>100</v>
+        <v>1100006</v>
       </c>
       <c r="C109" t="n">
         <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1100003</v>
+        <v>1100012</v>
       </c>
       <c r="C110" t="n">
         <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1100007</v>
+        <v>99</v>
       </c>
       <c r="C111" t="n">
         <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1100012</v>
+        <v>1100002</v>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
@@ -1939,111 +1939,111 @@
         <v>97</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1100009</v>
+        <v>1100003</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1100010</v>
+        <v>1100004</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1100011</v>
+        <v>1100007</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1100006</v>
+        <v>1100009</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1100012</v>
+        <v>1100010</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>99</v>
+        <v>1100012</v>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1100002</v>
+        <v>99</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2053,131 +2053,131 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>100</v>
+        <v>1110003</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1100003</v>
+        <v>1110004</v>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1100004</v>
+        <v>1110009</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1100007</v>
+        <v>1110011</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1100009</v>
+        <v>103</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1100012</v>
+        <v>102</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>99</v>
+        <v>1110008</v>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>104</v>
+        <v>1110001</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -2186,11 +2186,11 @@
         <v>1110003</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -2199,360 +2199,659 @@
         <v>1110004</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1110009</v>
+        <v>1110005</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1110011</v>
+        <v>1110006</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1110001</v>
+        <v>1110011</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>102</v>
+        <v>1110001</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1110008</v>
+        <v>1110002</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1110001</v>
+        <v>103</v>
       </c>
       <c r="C140" t="n">
         <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1110003</v>
+        <v>1110009</v>
       </c>
       <c r="C141" t="n">
         <v>2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1110005</v>
+        <v>1110003</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1110006</v>
+        <v>1110004</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>102</v>
+        <v>1110005</v>
       </c>
       <c r="C145" t="n">
         <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1110011</v>
+        <v>1110006</v>
       </c>
       <c r="C146" t="n">
         <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1110001</v>
+        <v>1110009</v>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1110002</v>
+        <v>1110011</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C149" t="n">
         <v>2</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1110009</v>
+        <v>1110002</v>
       </c>
       <c r="C150" t="n">
         <v>2</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>102</v>
+        <v>1110008</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1110003</v>
+        <v>107</v>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1110004</v>
+        <v>1120001</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1110005</v>
+        <v>1120002</v>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1110006</v>
+        <v>1120007</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1110009</v>
+        <v>1120010</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1110011</v>
+        <v>1120012</v>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1110002</v>
+        <v>108</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1110008</v>
+        <v>1120011</v>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>107</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>106</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>108</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>107</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>108</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>106</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3</v>
+      </c>
+      <c r="D183" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,6 +2857,448 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C206" t="n">
+        <v>2</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C208" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C209" t="n">
+        <v>2</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C210" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,20 +662,20 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
@@ -691,37 +691,37 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -730,37 +730,37 @@
         <v>98</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
@@ -769,20 +769,20 @@
         <v>980001</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -792,14 +792,14 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -808,37 +808,37 @@
         <v>990001</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
@@ -847,17 +847,17 @@
         <v>1000001</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -870,14 +870,14 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -886,37 +886,37 @@
         <v>1010001</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -925,37 +925,37 @@
         <v>1020001</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -964,37 +964,37 @@
         <v>1030001</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -1003,37 +1003,37 @@
         <v>1040001</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
@@ -1042,37 +1042,37 @@
         <v>1050001</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -1081,17 +1081,17 @@
         <v>1060001</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
@@ -1104,14 +1104,14 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1120,37 +1120,37 @@
         <v>1070001</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -1159,43 +1159,43 @@
         <v>1080001</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -1221,36 +1221,36 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1090004</v>
+        <v>1090010</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1090011</v>
+        <v>95</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1090010</v>
+        <v>1090002</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1090002</v>
+        <v>1090011</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
@@ -1286,36 +1286,36 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1090003</v>
+        <v>1090008</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1090011</v>
+        <v>1090009</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1090008</v>
+        <v>1090004</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1338,33 +1338,33 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1090010</v>
+        <v>1090012</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1090012</v>
+        <v>1090008</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>96</v>
+        <v>1090009</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1090008</v>
+        <v>95</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1442,36 +1442,36 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1090010</v>
+        <v>1090005</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1481,33 +1481,33 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090012</v>
+        <v>1090005</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C80" t="n">
         <v>2</v>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1090006</v>
+        <v>95</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1533,33 +1533,33 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>96</v>
+        <v>1090002</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C84" t="n">
         <v>3</v>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090004</v>
+        <v>1090009</v>
       </c>
       <c r="C86" t="n">
         <v>3</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C87" t="n">
         <v>3</v>
@@ -1611,33 +1611,33 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1090009</v>
+        <v>1100003</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>96</v>
+        <v>1100004</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1100003</v>
+        <v>1100009</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -1663,33 +1663,33 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1100009</v>
+        <v>100</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1100002</v>
+        <v>99</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -1715,36 +1715,36 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>99</v>
+        <v>1100011</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1100006</v>
+        <v>100</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1100011</v>
+        <v>1100003</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C100" t="n">
         <v>2</v>
@@ -1780,36 +1780,36 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1100003</v>
+        <v>1100012</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1100007</v>
+        <v>97</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1100012</v>
+        <v>1100004</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>97</v>
+        <v>1100009</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C105" t="n">
         <v>2</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1100009</v>
+        <v>1100011</v>
       </c>
       <c r="C106" t="n">
         <v>2</v>
@@ -1858,33 +1858,33 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1100010</v>
+        <v>1100006</v>
       </c>
       <c r="C107" t="n">
         <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1100011</v>
+        <v>1100012</v>
       </c>
       <c r="C108" t="n">
         <v>2</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1100006</v>
+        <v>99</v>
       </c>
       <c r="C109" t="n">
         <v>2</v>
@@ -1897,36 +1897,36 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1100012</v>
+        <v>1100002</v>
       </c>
       <c r="C110" t="n">
         <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C111" t="n">
         <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1100002</v>
+        <v>100</v>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>100</v>
+        <v>1100004</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1100003</v>
+        <v>1100007</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
@@ -1975,7 +1975,7 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1100004</v>
+        <v>1100009</v>
       </c>
       <c r="C116" t="n">
         <v>3</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C117" t="n">
         <v>3</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1100009</v>
+        <v>1100012</v>
       </c>
       <c r="C118" t="n">
         <v>3</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1100010</v>
+        <v>99</v>
       </c>
       <c r="C119" t="n">
         <v>3</v>
@@ -2027,33 +2027,33 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1100012</v>
+        <v>104</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>99</v>
+        <v>1110003</v>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>104</v>
+        <v>1110004</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1110003</v>
+        <v>1110009</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1110004</v>
+        <v>1110011</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -2092,62 +2092,62 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1110009</v>
+        <v>103</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1110011</v>
+        <v>1110001</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1110001</v>
+        <v>1110008</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>102</v>
+        <v>1110001</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1110008</v>
+        <v>1110003</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1110001</v>
+        <v>1110004</v>
       </c>
       <c r="C131" t="n">
         <v>2</v>
@@ -2183,36 +2183,36 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1110003</v>
+        <v>1110005</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1110004</v>
+        <v>1110006</v>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1110006</v>
+        <v>1110011</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>102</v>
+        <v>1110001</v>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -2248,36 +2248,36 @@
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1110011</v>
+        <v>1110002</v>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1110001</v>
+        <v>103</v>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1110002</v>
+        <v>1110009</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1110009</v>
+        <v>1110003</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>102</v>
+        <v>1110004</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
@@ -2326,36 +2326,36 @@
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1110003</v>
+        <v>1110005</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1110004</v>
+        <v>1110006</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1110005</v>
+        <v>1110009</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1110006</v>
+        <v>1110011</v>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -2378,33 +2378,33 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1110009</v>
+        <v>104</v>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1110011</v>
+        <v>1110002</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>104</v>
+        <v>1110008</v>
       </c>
       <c r="C149" t="n">
         <v>2</v>
@@ -2417,33 +2417,33 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1110002</v>
+        <v>107</v>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1110008</v>
+        <v>1120001</v>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>107</v>
+        <v>1120002</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -2456,7 +2456,7 @@
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1120001</v>
+        <v>1120007</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1120002</v>
+        <v>1120010</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1120007</v>
+        <v>1120012</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -2495,33 +2495,33 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1120010</v>
+        <v>106</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1120012</v>
+        <v>108</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>106</v>
+        <v>1120011</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1120011</v>
+        <v>1120001</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>107</v>
+        <v>1120002</v>
       </c>
       <c r="C161" t="n">
         <v>2</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1120001</v>
+        <v>1120012</v>
       </c>
       <c r="C162" t="n">
         <v>2</v>
@@ -2586,36 +2586,36 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1120002</v>
+        <v>1120006</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1120012</v>
+        <v>106</v>
       </c>
       <c r="C164" t="n">
         <v>2</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -2625,36 +2625,36 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>106</v>
+        <v>1120004</v>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1120007</v>
+        <v>108</v>
       </c>
       <c r="C167" t="n">
         <v>2</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1120004</v>
+        <v>1120011</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>108</v>
+        <v>1120012</v>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -2677,36 +2677,36 @@
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1120011</v>
+        <v>1120003</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1120012</v>
+        <v>1120004</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1120003</v>
+        <v>1120002</v>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1120004</v>
+        <v>1120007</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -2729,33 +2729,33 @@
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1120007</v>
+        <v>1120006</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1120003</v>
+        <v>1120010</v>
       </c>
       <c r="C176" t="n">
         <v>2</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1120006</v>
+        <v>107</v>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>1120010</v>
+        <v>108</v>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>107</v>
+        <v>1120004</v>
       </c>
       <c r="C179" t="n">
         <v>3</v>
@@ -2807,59 +2807,59 @@
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C180" t="n">
         <v>3</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1120004</v>
+        <v>1120003</v>
       </c>
       <c r="C181" t="n">
         <v>3</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>106</v>
+        <v>1130004</v>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1120003</v>
+        <v>1130005</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1130004</v>
+        <v>1130010</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1130005</v>
+        <v>1130011</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -2885,33 +2885,33 @@
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1130010</v>
+        <v>1130003</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1130011</v>
+        <v>1130006</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1130003</v>
+        <v>1130007</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1130006</v>
+        <v>1130008</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1130007</v>
+        <v>1130012</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1130008</v>
+        <v>1130004</v>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1130012</v>
+        <v>1130005</v>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>1130004</v>
+        <v>1130010</v>
       </c>
       <c r="C193" t="n">
         <v>2</v>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1130005</v>
+        <v>1130011</v>
       </c>
       <c r="C194" t="n">
         <v>2</v>
@@ -3002,36 +3002,36 @@
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1130010</v>
+        <v>1130001</v>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1130011</v>
+        <v>1130002</v>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1130001</v>
+        <v>1130003</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1130002</v>
+        <v>1130006</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1130006</v>
+        <v>1130005</v>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1130004</v>
+        <v>1130010</v>
       </c>
       <c r="C201" t="n">
         <v>3</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1130005</v>
+        <v>1130011</v>
       </c>
       <c r="C202" t="n">
         <v>3</v>
@@ -3106,36 +3106,36 @@
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1130010</v>
+        <v>1130001</v>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1130001</v>
+        <v>1130003</v>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -3145,33 +3145,33 @@
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1130012</v>
+        <v>1130002</v>
       </c>
       <c r="C206" t="n">
         <v>2</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1130003</v>
+        <v>1130007</v>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1130002</v>
+        <v>1130008</v>
       </c>
       <c r="C208" t="n">
         <v>2</v>
@@ -3184,10 +3184,10 @@
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1130007</v>
+        <v>1130006</v>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1130008</v>
+        <v>1130012</v>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -3210,36 +3210,36 @@
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1130006</v>
+        <v>1130009</v>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1130012</v>
+        <v>1130001</v>
       </c>
       <c r="C212" t="n">
         <v>3</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1130009</v>
+        <v>1130008</v>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -3249,51 +3249,454 @@
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1130001</v>
+        <v>1130009</v>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1130008</v>
+        <v>1130002</v>
       </c>
       <c r="C215" t="n">
         <v>3</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1130009</v>
+        <v>1140006</v>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1130002</v>
+        <v>1140007</v>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D217" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C222" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C224" t="n">
+        <v>2</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C225" t="n">
+        <v>2</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>110</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>110</v>
+      </c>
+      <c r="C235" t="n">
+        <v>2</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C238" t="n">
+        <v>2</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C239" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C240" t="n">
+        <v>2</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C244" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C245" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3</v>
+      </c>
+      <c r="D248" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J248"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,46 +662,46 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -714,20 +714,20 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -740,72 +740,72 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -818,98 +818,98 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C34" t="n">
         <v>2</v>
@@ -922,33 +922,33 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C35" t="n">
         <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
@@ -961,59 +961,59 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1026,20 +1026,20 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
@@ -1052,33 +1052,33 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C47" t="n">
         <v>2</v>
@@ -1091,36 +1091,36 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -1143,33 +1143,33 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1080001</v>
+        <v>1090004</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1090002</v>
+        <v>1090011</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -1182,49 +1182,49 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1090003</v>
+        <v>1090010</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1090004</v>
+        <v>95</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1090011</v>
+        <v>1090002</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1090010</v>
+        <v>1090003</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1247,49 +1247,49 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1090002</v>
+        <v>1090008</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1090003</v>
+        <v>1090009</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1090011</v>
+        <v>1090004</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1299,49 +1299,49 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1090009</v>
+        <v>1090006</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1090004</v>
+        <v>1090012</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1090010</v>
+        <v>96</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1090012</v>
+        <v>1090009</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1090009</v>
+        <v>1090011</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1403,40 +1403,40 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>95</v>
+        <v>1090005</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1090010</v>
+        <v>1090012</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1090011</v>
+        <v>1090008</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1445,46 +1445,46 @@
         <v>1090005</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1090012</v>
+        <v>1090006</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1090008</v>
+        <v>96</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090005</v>
+        <v>95</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1494,46 +1494,46 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1090006</v>
+        <v>1090002</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C81" t="n">
         <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1090002</v>
+        <v>1090006</v>
       </c>
       <c r="C82" t="n">
         <v>3</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090003</v>
+        <v>1090009</v>
       </c>
       <c r="C83" t="n">
         <v>3</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C84" t="n">
         <v>3</v>
@@ -1572,46 +1572,46 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090006</v>
+        <v>1100003</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090009</v>
+        <v>1100004</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>96</v>
+        <v>1100009</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1100003</v>
+        <v>1100010</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -1624,46 +1624,46 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1100009</v>
+        <v>1100002</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -1676,49 +1676,49 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1100002</v>
+        <v>1100006</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1100007</v>
+        <v>1100011</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1100006</v>
+        <v>1100003</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1100011</v>
+        <v>1100007</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -1741,49 +1741,49 @@
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>100</v>
+        <v>1100012</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1100003</v>
+        <v>97</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1100007</v>
+        <v>1100004</v>
       </c>
       <c r="C100" t="n">
         <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1100012</v>
+        <v>1100009</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>97</v>
+        <v>1100010</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1100004</v>
+        <v>1100011</v>
       </c>
       <c r="C103" t="n">
         <v>2</v>
@@ -1819,88 +1819,88 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1100009</v>
+        <v>1100006</v>
       </c>
       <c r="C104" t="n">
         <v>2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C105" t="n">
         <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1100011</v>
+        <v>99</v>
       </c>
       <c r="C106" t="n">
         <v>2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1100006</v>
+        <v>1100002</v>
       </c>
       <c r="C107" t="n">
         <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1100012</v>
+        <v>97</v>
       </c>
       <c r="C108" t="n">
         <v>2</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1100002</v>
+        <v>1100003</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C112" t="n">
         <v>3</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1100003</v>
+        <v>1100009</v>
       </c>
       <c r="C113" t="n">
         <v>3</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1100007</v>
+        <v>1100012</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
@@ -1975,7 +1975,7 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1100009</v>
+        <v>99</v>
       </c>
       <c r="C116" t="n">
         <v>3</v>
@@ -1988,46 +1988,46 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1100010</v>
+        <v>104</v>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1100012</v>
+        <v>1110003</v>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>99</v>
+        <v>1110004</v>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>104</v>
+        <v>1110009</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1110003</v>
+        <v>1110011</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -2053,53 +2053,53 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1110004</v>
+        <v>103</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1110009</v>
+        <v>1110001</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1110011</v>
+        <v>102</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>103</v>
+        <v>1110008</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
@@ -2108,20 +2108,20 @@
         <v>1110001</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>102</v>
+        <v>1110003</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1110008</v>
+        <v>1110004</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -2144,49 +2144,49 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1110001</v>
+        <v>1110005</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1110003</v>
+        <v>1110006</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C131" t="n">
         <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1110005</v>
+        <v>1110011</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1110006</v>
+        <v>1110001</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -2209,49 +2209,49 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>102</v>
+        <v>1110002</v>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1110011</v>
+        <v>103</v>
       </c>
       <c r="C135" t="n">
         <v>2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1110001</v>
+        <v>1110009</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1110002</v>
+        <v>102</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>103</v>
+        <v>1110003</v>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1110009</v>
+        <v>1110004</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -2287,49 +2287,49 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>102</v>
+        <v>1110005</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1110003</v>
+        <v>1110006</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1110004</v>
+        <v>1110009</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1110005</v>
+        <v>1110011</v>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -2339,85 +2339,85 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1110006</v>
+        <v>104</v>
       </c>
       <c r="C144" t="n">
         <v>2</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1110009</v>
+        <v>1110002</v>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1110011</v>
+        <v>1110008</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1110002</v>
+        <v>1120001</v>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1110008</v>
+        <v>1120002</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>107</v>
+        <v>1120007</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1120001</v>
+        <v>1120010</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1120002</v>
+        <v>1120012</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -2456,49 +2456,49 @@
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1120007</v>
+        <v>106</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1120010</v>
+        <v>108</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1120012</v>
+        <v>1120011</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>108</v>
+        <v>1120001</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1120011</v>
+        <v>1120002</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>107</v>
+        <v>1120012</v>
       </c>
       <c r="C159" t="n">
         <v>2</v>
@@ -2547,88 +2547,88 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1120001</v>
+        <v>1120006</v>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1120002</v>
+        <v>106</v>
       </c>
       <c r="C161" t="n">
         <v>2</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1120012</v>
+        <v>1120007</v>
       </c>
       <c r="C162" t="n">
         <v>2</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1120006</v>
+        <v>1120004</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C164" t="n">
         <v>2</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1120007</v>
+        <v>1120011</v>
       </c>
       <c r="C165" t="n">
         <v>2</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1120004</v>
+        <v>1120012</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -2638,49 +2638,49 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>108</v>
+        <v>1120003</v>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1120011</v>
+        <v>1120004</v>
       </c>
       <c r="C168" t="n">
         <v>2</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1120012</v>
+        <v>1120002</v>
       </c>
       <c r="C169" t="n">
         <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1120003</v>
+        <v>1120007</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -2690,49 +2690,49 @@
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1120004</v>
+        <v>1120003</v>
       </c>
       <c r="C171" t="n">
         <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1120002</v>
+        <v>1120006</v>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1120007</v>
+        <v>1120010</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1120003</v>
+        <v>107</v>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1120006</v>
+        <v>108</v>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1120010</v>
+        <v>1120004</v>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -2768,72 +2768,72 @@
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C177" t="n">
         <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>108</v>
+        <v>1120003</v>
       </c>
       <c r="C178" t="n">
         <v>3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1120004</v>
+        <v>1130004</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>106</v>
+        <v>1130005</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1120003</v>
+        <v>1130010</v>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1130004</v>
+        <v>1130011</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -2846,46 +2846,46 @@
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1130005</v>
+        <v>1130003</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1130010</v>
+        <v>1130006</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1130011</v>
+        <v>1130007</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1130003</v>
+        <v>1130008</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1130006</v>
+        <v>1130012</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1130007</v>
+        <v>1130004</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1130008</v>
+        <v>1130005</v>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1130012</v>
+        <v>1130010</v>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1130004</v>
+        <v>1130011</v>
       </c>
       <c r="C191" t="n">
         <v>2</v>
@@ -2963,49 +2963,49 @@
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1130005</v>
+        <v>1130001</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>1130010</v>
+        <v>1130002</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1130011</v>
+        <v>1130003</v>
       </c>
       <c r="C194" t="n">
         <v>2</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1130001</v>
+        <v>1130006</v>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1130002</v>
+        <v>1130004</v>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1130003</v>
+        <v>1130005</v>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1130006</v>
+        <v>1130010</v>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1130004</v>
+        <v>1130011</v>
       </c>
       <c r="C199" t="n">
         <v>3</v>
@@ -3067,88 +3067,88 @@
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1130005</v>
+        <v>1130001</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1130010</v>
+        <v>1130012</v>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1130011</v>
+        <v>1130003</v>
       </c>
       <c r="C202" t="n">
         <v>3</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C203" t="n">
         <v>2</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1130012</v>
+        <v>1130007</v>
       </c>
       <c r="C204" t="n">
         <v>2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1130003</v>
+        <v>1130008</v>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1130002</v>
+        <v>1130006</v>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1130007</v>
+        <v>1130012</v>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -3171,40 +3171,40 @@
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1130008</v>
+        <v>1130009</v>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1130006</v>
+        <v>1130001</v>
       </c>
       <c r="C209" t="n">
         <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1130012</v>
+        <v>1130008</v>
       </c>
       <c r="C210" t="n">
         <v>3</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
@@ -3213,69 +3213,69 @@
         <v>1130009</v>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C212" t="n">
         <v>3</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1130008</v>
+        <v>1140006</v>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1130009</v>
+        <v>1140007</v>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1130002</v>
+        <v>1140008</v>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1140006</v>
+        <v>1140010</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -3288,49 +3288,49 @@
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1140007</v>
+        <v>1140004</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>1140008</v>
+        <v>1140005</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>1140010</v>
+        <v>1140006</v>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>1140004</v>
+        <v>1140007</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>1140005</v>
+        <v>1140008</v>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>1140006</v>
+        <v>1140010</v>
       </c>
       <c r="C222" t="n">
         <v>2</v>
@@ -3366,49 +3366,49 @@
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1140007</v>
+        <v>1140009</v>
       </c>
       <c r="C223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>1140008</v>
+        <v>1140012</v>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>1140010</v>
+        <v>1140006</v>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>1140009</v>
+        <v>1140007</v>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>1140012</v>
+        <v>1140008</v>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -3431,88 +3431,88 @@
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>1140006</v>
+        <v>110</v>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>1140007</v>
+        <v>1140002</v>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>1140008</v>
+        <v>1140003</v>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>110</v>
+        <v>1140001</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>1140002</v>
+        <v>110</v>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="B233" t="n">
-        <v>1140003</v>
+        <v>1140002</v>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="B234" t="n">
-        <v>1140001</v>
+        <v>1140003</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>110</v>
+        <v>1140012</v>
       </c>
       <c r="C235" t="n">
         <v>2</v>
@@ -3535,49 +3535,49 @@
     </row>
     <row r="236">
       <c r="B236" t="n">
-        <v>1140002</v>
+        <v>1140004</v>
       </c>
       <c r="C236" t="n">
         <v>2</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="B237" t="n">
-        <v>1140003</v>
+        <v>1140005</v>
       </c>
       <c r="C237" t="n">
         <v>2</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="B238" t="n">
-        <v>1140012</v>
+        <v>1140002</v>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="B239" t="n">
-        <v>1140004</v>
+        <v>1140003</v>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="240">
       <c r="B240" t="n">
-        <v>1140005</v>
+        <v>1140010</v>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -3600,49 +3600,49 @@
     </row>
     <row r="241">
       <c r="B241" t="n">
-        <v>1140002</v>
+        <v>1140001</v>
       </c>
       <c r="C241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="B242" t="n">
-        <v>1140003</v>
+        <v>1140009</v>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="B243" t="n">
-        <v>1140010</v>
+        <v>1140004</v>
       </c>
       <c r="C243" t="n">
         <v>3</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="B244" t="n">
-        <v>1140001</v>
+        <v>1140005</v>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="245">
       <c r="B245" t="n">
-        <v>1140009</v>
+        <v>1140012</v>
       </c>
       <c r="C245" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -3665,38 +3665,103 @@
     </row>
     <row r="246">
       <c r="B246" t="n">
-        <v>1140004</v>
+        <v>1150002</v>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="B247" t="n">
-        <v>1140005</v>
+        <v>1150003</v>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="B248" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D248" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>111</v>
+      </c>
+      <c r="C250" t="n">
+        <v>2</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>111</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3</v>
+      </c>
+      <c r="D253" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>

--- a/config/data/EnemyWeakness.xlsx
+++ b/config/data/EnemyWeakness.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,137 +571,137 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -714,111 +714,111 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>105</v>
+        <v>980001</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>106</v>
+        <v>990001</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>107</v>
+        <v>1000001</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
@@ -831,88 +831,88 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>108</v>
+        <v>1010001</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>109</v>
+        <v>1020001</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>109</v>
+        <v>1030001</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>110</v>
+        <v>1030001</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -922,20 +922,20 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>110</v>
+        <v>1030001</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>111</v>
+        <v>1040001</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -948,101 +948,101 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>111</v>
+        <v>1040001</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>111</v>
+        <v>1040001</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>95</v>
+        <v>1050001</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>95</v>
+        <v>1050001</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>95</v>
+        <v>1050001</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>96</v>
+        <v>1060001</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>96</v>
+        <v>1060001</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>96</v>
+        <v>1060001</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1052,103 +1052,2716 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>97</v>
+        <v>1070001</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>97</v>
+        <v>1070001</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>98</v>
+        <v>1070001</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>98</v>
+        <v>1080001</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>98</v>
+        <v>1080001</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>99</v>
+        <v>1080001</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>99</v>
+        <v>1090002</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>95</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>96</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>95</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>96</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>95</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>96</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>100</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
         <v>99</v>
       </c>
-      <c r="C52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>100</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>99</v>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>97</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>100</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>99</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>104</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>103</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>102</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>102</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>103</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>102</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C141" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>104</v>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>107</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>106</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>108</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>107</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>106</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>108</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>107</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>108</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>106</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C204" t="n">
+        <v>2</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C211" t="n">
+        <v>2</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C219" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C220" t="n">
+        <v>2</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C221" t="n">
+        <v>2</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C222" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>110</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>110</v>
+      </c>
+      <c r="C232" t="n">
+        <v>2</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C233" t="n">
+        <v>2</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C234" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C235" t="n">
+        <v>2</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>111</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>111</v>
+      </c>
+      <c r="C250" t="n">
+        <v>2</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>111</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3</v>
+      </c>
+      <c r="D253" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
